--- a/omicron/xlsx/7SD82-DIF-test-plan.xlsx
+++ b/omicron/xlsx/7SD82-DIF-test-plan.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>generated 2026-09-05 12:28 from 7SD82.html</t>
+          <t>generated 2026-09-15 01:49 from src/7sd82-dif.html</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>kv=110; freq=50; len=15; type=cable; iref=600; ich=25; ctAp=600; ctAs=1; ctAstar=line; ctBp=600; ctBs=1; ctBstar=line; stage=local; vtp=110000; vts=100; vtc=wye; comm=fibre; tprop=0.5; tasym=0.2; sync=pp; cmc=6x; imax=12.5; vmax=300</t>
+          <t>kv=110; freq=50; rot=ABC; len=15; type=cable; iref=600; ich=25; ctAp=600; ctAs=1; ctAstar=line; ctBp=600; ctBs=1; ctBstar=line; stage=local; vtp=110000; vts=100; vtc=wye; comm=fibre; tprop=0.5; tasym=0.2; sync=pp; cmc=6x; imax=12.5; vmax=300</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="F4" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — above</t>
+          <t>Slope at Irest 1 pu — above</t>
         </is>
       </c>
       <c r="G4" s="11" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — below</t>
+          <t>Slope at Irest 1 pu — below</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — above</t>
+          <t>Slope at Irest 3 pu — above</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — below</t>
+          <t>Slope at Irest 3 pu — below</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — above</t>
+          <t>Slope at Irest 8 pu — above</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — below</t>
+          <t>Slope at Irest 8 pu — below</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
-          <t>Both ends matched and opposed at 8.0 pu — an external fault. This is the polarity and ratio test.</t>
+          <t>Both ends matched and opposed at 8 pu — an external fault. This is the polarity and ratio test.</t>
         </is>
       </c>
       <c r="H10" s="12" t="n"/>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="G14" s="15" t="inlineStr">
         <is>
-          <t>Both ends matched and opposed at 4.0 pu residual</t>
+          <t>Both ends matched and opposed at 4 pu residual</t>
         </is>
       </c>
       <c r="H14" s="16" t="n"/>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="F30" s="15" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="G30" s="15" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× threshold</t>
+          <t>Timing at 3× threshold</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× threshold</t>
+          <t>Timing at 5× threshold</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="F38" s="15" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="G38" s="15" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="G44" s="15" t="inlineStr">
         <is>
-          <t>Internal fault at end A, 4.0 × In</t>
+          <t>Internal fault at end A, 4 × In</t>
         </is>
       </c>
       <c r="H44" s="16" t="n">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="F63" s="15" t="inlineStr">
         <is>
-          <t>Timing at 0.50× threshold</t>
+          <t>Timing at 0.5× threshold</t>
         </is>
       </c>
       <c r="G63" s="15" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="F66" s="11" t="inlineStr">
         <is>
-          <t>Timing at 1.30× threshold</t>
+          <t>Timing at 1.3× threshold</t>
         </is>
       </c>
       <c r="G66" s="11" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — above</t>
+          <t>Slope at Irest 1 pu — above</t>
         </is>
       </c>
       <c r="H20" s="12" t="n"/>
@@ -9165,7 +9165,7 @@
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — above</t>
+          <t>Slope at Irest 1 pu — above</t>
         </is>
       </c>
       <c r="H21" s="12" t="n"/>
@@ -9244,7 +9244,7 @@
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — above</t>
+          <t>Slope at Irest 1 pu — above</t>
         </is>
       </c>
       <c r="H22" s="12" t="n"/>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — above</t>
+          <t>Slope at Irest 1 pu — above</t>
         </is>
       </c>
       <c r="H23" s="12" t="n"/>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — above</t>
+          <t>Slope at Irest 1 pu — above</t>
         </is>
       </c>
       <c r="H24" s="12" t="n"/>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — above</t>
+          <t>Slope at Irest 1 pu — above</t>
         </is>
       </c>
       <c r="H25" s="12" t="n"/>
@@ -9572,7 +9572,7 @@
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — above</t>
+          <t>Slope at Irest 1 pu — above</t>
         </is>
       </c>
       <c r="H26" s="12" t="n"/>
@@ -9655,7 +9655,7 @@
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — above</t>
+          <t>Slope at Irest 1 pu — above</t>
         </is>
       </c>
       <c r="H27" s="12" t="n"/>
@@ -9738,7 +9738,7 @@
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — above</t>
+          <t>Slope at Irest 1 pu — above</t>
         </is>
       </c>
       <c r="H28" s="12" t="n"/>
@@ -9821,7 +9821,7 @@
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — below</t>
+          <t>Slope at Irest 1 pu — below</t>
         </is>
       </c>
       <c r="H29" s="12" t="n"/>
@@ -9900,7 +9900,7 @@
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — below</t>
+          <t>Slope at Irest 1 pu — below</t>
         </is>
       </c>
       <c r="H30" s="12" t="n"/>
@@ -9979,7 +9979,7 @@
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — below</t>
+          <t>Slope at Irest 1 pu — below</t>
         </is>
       </c>
       <c r="H31" s="12" t="n"/>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — below</t>
+          <t>Slope at Irest 1 pu — below</t>
         </is>
       </c>
       <c r="H32" s="12" t="n"/>
@@ -10141,7 +10141,7 @@
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — below</t>
+          <t>Slope at Irest 1 pu — below</t>
         </is>
       </c>
       <c r="H33" s="12" t="n"/>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — below</t>
+          <t>Slope at Irest 1 pu — below</t>
         </is>
       </c>
       <c r="H34" s="12" t="n"/>
@@ -10307,7 +10307,7 @@
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — below</t>
+          <t>Slope at Irest 1 pu — below</t>
         </is>
       </c>
       <c r="H35" s="12" t="n"/>
@@ -10390,7 +10390,7 @@
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — below</t>
+          <t>Slope at Irest 1 pu — below</t>
         </is>
       </c>
       <c r="H36" s="12" t="n"/>
@@ -10473,7 +10473,7 @@
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — below</t>
+          <t>Slope at Irest 1 pu — below</t>
         </is>
       </c>
       <c r="H37" s="12" t="n"/>
@@ -10556,7 +10556,7 @@
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — above</t>
+          <t>Slope at Irest 3 pu — above</t>
         </is>
       </c>
       <c r="H38" s="12" t="n"/>
@@ -10635,7 +10635,7 @@
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — above</t>
+          <t>Slope at Irest 3 pu — above</t>
         </is>
       </c>
       <c r="H39" s="12" t="n"/>
@@ -10714,7 +10714,7 @@
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — above</t>
+          <t>Slope at Irest 3 pu — above</t>
         </is>
       </c>
       <c r="H40" s="12" t="n"/>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — above</t>
+          <t>Slope at Irest 3 pu — above</t>
         </is>
       </c>
       <c r="H41" s="12" t="n"/>
@@ -10876,7 +10876,7 @@
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — above</t>
+          <t>Slope at Irest 3 pu — above</t>
         </is>
       </c>
       <c r="H42" s="12" t="n"/>
@@ -10959,7 +10959,7 @@
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — above</t>
+          <t>Slope at Irest 3 pu — above</t>
         </is>
       </c>
       <c r="H43" s="12" t="n"/>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — above</t>
+          <t>Slope at Irest 3 pu — above</t>
         </is>
       </c>
       <c r="H44" s="12" t="n"/>
@@ -11125,7 +11125,7 @@
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — above</t>
+          <t>Slope at Irest 3 pu — above</t>
         </is>
       </c>
       <c r="H45" s="12" t="n"/>
@@ -11208,7 +11208,7 @@
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — above</t>
+          <t>Slope at Irest 3 pu — above</t>
         </is>
       </c>
       <c r="H46" s="12" t="n"/>
@@ -11291,7 +11291,7 @@
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — below</t>
+          <t>Slope at Irest 3 pu — below</t>
         </is>
       </c>
       <c r="H47" s="12" t="n"/>
@@ -11370,7 +11370,7 @@
       </c>
       <c r="G48" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — below</t>
+          <t>Slope at Irest 3 pu — below</t>
         </is>
       </c>
       <c r="H48" s="12" t="n"/>
@@ -11449,7 +11449,7 @@
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — below</t>
+          <t>Slope at Irest 3 pu — below</t>
         </is>
       </c>
       <c r="H49" s="12" t="n"/>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — below</t>
+          <t>Slope at Irest 3 pu — below</t>
         </is>
       </c>
       <c r="H50" s="12" t="n"/>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — below</t>
+          <t>Slope at Irest 3 pu — below</t>
         </is>
       </c>
       <c r="H51" s="12" t="n"/>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="G52" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — below</t>
+          <t>Slope at Irest 3 pu — below</t>
         </is>
       </c>
       <c r="H52" s="12" t="n"/>
@@ -11777,7 +11777,7 @@
       </c>
       <c r="G53" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — below</t>
+          <t>Slope at Irest 3 pu — below</t>
         </is>
       </c>
       <c r="H53" s="12" t="n"/>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="G54" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — below</t>
+          <t>Slope at Irest 3 pu — below</t>
         </is>
       </c>
       <c r="H54" s="12" t="n"/>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="G55" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — below</t>
+          <t>Slope at Irest 3 pu — below</t>
         </is>
       </c>
       <c r="H55" s="12" t="n"/>
@@ -12026,7 +12026,7 @@
       </c>
       <c r="G56" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — above</t>
+          <t>Slope at Irest 8 pu — above</t>
         </is>
       </c>
       <c r="H56" s="12" t="n"/>
@@ -12105,7 +12105,7 @@
       </c>
       <c r="G57" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — above</t>
+          <t>Slope at Irest 8 pu — above</t>
         </is>
       </c>
       <c r="H57" s="12" t="n"/>
@@ -12184,7 +12184,7 @@
       </c>
       <c r="G58" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — above</t>
+          <t>Slope at Irest 8 pu — above</t>
         </is>
       </c>
       <c r="H58" s="12" t="n"/>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="G59" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — above</t>
+          <t>Slope at Irest 8 pu — above</t>
         </is>
       </c>
       <c r="H59" s="12" t="n"/>
@@ -12346,7 +12346,7 @@
       </c>
       <c r="G60" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — above</t>
+          <t>Slope at Irest 8 pu — above</t>
         </is>
       </c>
       <c r="H60" s="12" t="n"/>
@@ -12429,7 +12429,7 @@
       </c>
       <c r="G61" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — above</t>
+          <t>Slope at Irest 8 pu — above</t>
         </is>
       </c>
       <c r="H61" s="12" t="n"/>
@@ -12512,7 +12512,7 @@
       </c>
       <c r="G62" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — above</t>
+          <t>Slope at Irest 8 pu — above</t>
         </is>
       </c>
       <c r="H62" s="12" t="n"/>
@@ -12595,7 +12595,7 @@
       </c>
       <c r="G63" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — above</t>
+          <t>Slope at Irest 8 pu — above</t>
         </is>
       </c>
       <c r="H63" s="12" t="n"/>
@@ -12678,7 +12678,7 @@
       </c>
       <c r="G64" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — above</t>
+          <t>Slope at Irest 8 pu — above</t>
         </is>
       </c>
       <c r="H64" s="12" t="n"/>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="G65" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — below</t>
+          <t>Slope at Irest 8 pu — below</t>
         </is>
       </c>
       <c r="H65" s="12" t="n"/>
@@ -12840,7 +12840,7 @@
       </c>
       <c r="G66" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — below</t>
+          <t>Slope at Irest 8 pu — below</t>
         </is>
       </c>
       <c r="H66" s="12" t="n"/>
@@ -12919,7 +12919,7 @@
       </c>
       <c r="G67" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — below</t>
+          <t>Slope at Irest 8 pu — below</t>
         </is>
       </c>
       <c r="H67" s="12" t="n"/>
@@ -12998,7 +12998,7 @@
       </c>
       <c r="G68" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — below</t>
+          <t>Slope at Irest 8 pu — below</t>
         </is>
       </c>
       <c r="H68" s="12" t="n"/>
@@ -13081,7 +13081,7 @@
       </c>
       <c r="G69" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — below</t>
+          <t>Slope at Irest 8 pu — below</t>
         </is>
       </c>
       <c r="H69" s="12" t="n"/>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="G70" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — below</t>
+          <t>Slope at Irest 8 pu — below</t>
         </is>
       </c>
       <c r="H70" s="12" t="n"/>
@@ -13247,7 +13247,7 @@
       </c>
       <c r="G71" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — below</t>
+          <t>Slope at Irest 8 pu — below</t>
         </is>
       </c>
       <c r="H71" s="12" t="n"/>
@@ -13330,7 +13330,7 @@
       </c>
       <c r="G72" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — below</t>
+          <t>Slope at Irest 8 pu — below</t>
         </is>
       </c>
       <c r="H72" s="12" t="n"/>
@@ -13413,7 +13413,7 @@
       </c>
       <c r="G73" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — below</t>
+          <t>Slope at Irest 8 pu — below</t>
         </is>
       </c>
       <c r="H73" s="12" t="n"/>
@@ -20918,7 +20918,7 @@
       </c>
       <c r="G168" s="15" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H168" s="16" t="n"/>
@@ -20993,7 +20993,7 @@
       </c>
       <c r="G169" s="15" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H169" s="16" t="n"/>
@@ -21068,7 +21068,7 @@
       </c>
       <c r="G170" s="15" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H170" s="16" t="n"/>
@@ -21143,7 +21143,7 @@
       </c>
       <c r="G171" s="15" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H171" s="16" t="n"/>
@@ -21222,7 +21222,7 @@
       </c>
       <c r="G172" s="15" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H172" s="16" t="n"/>
@@ -21301,7 +21301,7 @@
       </c>
       <c r="G173" s="15" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H173" s="16" t="n"/>
@@ -22304,7 +22304,7 @@
       </c>
       <c r="G186" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H186" s="12" t="n"/>
@@ -22379,7 +22379,7 @@
       </c>
       <c r="G187" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H187" s="12" t="n"/>
@@ -22454,7 +22454,7 @@
       </c>
       <c r="G188" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H188" s="12" t="n"/>
@@ -22529,7 +22529,7 @@
       </c>
       <c r="G189" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H189" s="12" t="n"/>
@@ -22608,7 +22608,7 @@
       </c>
       <c r="G190" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H190" s="12" t="n"/>
@@ -22687,7 +22687,7 @@
       </c>
       <c r="G191" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H191" s="12" t="n"/>
@@ -22766,7 +22766,7 @@
       </c>
       <c r="G192" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× threshold</t>
+          <t>Timing at 3× threshold</t>
         </is>
       </c>
       <c r="H192" s="12" t="n"/>
@@ -22841,7 +22841,7 @@
       </c>
       <c r="G193" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× threshold</t>
+          <t>Timing at 3× threshold</t>
         </is>
       </c>
       <c r="H193" s="12" t="n"/>
@@ -22916,7 +22916,7 @@
       </c>
       <c r="G194" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× threshold</t>
+          <t>Timing at 3× threshold</t>
         </is>
       </c>
       <c r="H194" s="12" t="n"/>
@@ -22991,7 +22991,7 @@
       </c>
       <c r="G195" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× threshold</t>
+          <t>Timing at 3× threshold</t>
         </is>
       </c>
       <c r="H195" s="12" t="n"/>
@@ -23070,7 +23070,7 @@
       </c>
       <c r="G196" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× threshold</t>
+          <t>Timing at 3× threshold</t>
         </is>
       </c>
       <c r="H196" s="12" t="n"/>
@@ -23149,7 +23149,7 @@
       </c>
       <c r="G197" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× threshold</t>
+          <t>Timing at 3× threshold</t>
         </is>
       </c>
       <c r="H197" s="12" t="n"/>
@@ -23228,7 +23228,7 @@
       </c>
       <c r="G198" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× threshold</t>
+          <t>Timing at 5× threshold</t>
         </is>
       </c>
       <c r="H198" s="12" t="n"/>
@@ -23303,7 +23303,7 @@
       </c>
       <c r="G199" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× threshold</t>
+          <t>Timing at 5× threshold</t>
         </is>
       </c>
       <c r="H199" s="12" t="n"/>
@@ -23378,7 +23378,7 @@
       </c>
       <c r="G200" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× threshold</t>
+          <t>Timing at 5× threshold</t>
         </is>
       </c>
       <c r="H200" s="12" t="n"/>
@@ -23453,7 +23453,7 @@
       </c>
       <c r="G201" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× threshold</t>
+          <t>Timing at 5× threshold</t>
         </is>
       </c>
       <c r="H201" s="12" t="n"/>
@@ -23532,7 +23532,7 @@
       </c>
       <c r="G202" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× threshold</t>
+          <t>Timing at 5× threshold</t>
         </is>
       </c>
       <c r="H202" s="12" t="n"/>
@@ -23611,7 +23611,7 @@
       </c>
       <c r="G203" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× threshold</t>
+          <t>Timing at 5× threshold</t>
         </is>
       </c>
       <c r="H203" s="12" t="n"/>
@@ -24614,7 +24614,7 @@
       </c>
       <c r="G216" s="15" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H216" s="16" t="n"/>
@@ -24689,7 +24689,7 @@
       </c>
       <c r="G217" s="15" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H217" s="16" t="n"/>
@@ -24764,7 +24764,7 @@
       </c>
       <c r="G218" s="15" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H218" s="16" t="n"/>
@@ -24839,7 +24839,7 @@
       </c>
       <c r="G219" s="15" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H219" s="16" t="n"/>
@@ -24918,7 +24918,7 @@
       </c>
       <c r="G220" s="15" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H220" s="16" t="n"/>
@@ -24997,7 +24997,7 @@
       </c>
       <c r="G221" s="15" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H221" s="16" t="n"/>
@@ -36109,7 +36109,7 @@
       </c>
       <c r="G361" s="15" t="inlineStr">
         <is>
-          <t>Timing at 0.50× threshold</t>
+          <t>Timing at 0.5× threshold</t>
         </is>
       </c>
       <c r="H361" s="16" t="n"/>
@@ -36188,7 +36188,7 @@
       </c>
       <c r="G362" s="15" t="inlineStr">
         <is>
-          <t>Timing at 0.50× threshold</t>
+          <t>Timing at 0.5× threshold</t>
         </is>
       </c>
       <c r="H362" s="16" t="n"/>
@@ -36263,7 +36263,7 @@
       </c>
       <c r="G363" s="15" t="inlineStr">
         <is>
-          <t>Timing at 0.50× threshold</t>
+          <t>Timing at 0.5× threshold</t>
         </is>
       </c>
       <c r="H363" s="16" t="n"/>
@@ -36338,7 +36338,7 @@
       </c>
       <c r="G364" s="15" t="inlineStr">
         <is>
-          <t>Timing at 0.50× threshold</t>
+          <t>Timing at 0.5× threshold</t>
         </is>
       </c>
       <c r="H364" s="16" t="n"/>
@@ -36417,7 +36417,7 @@
       </c>
       <c r="G365" s="15" t="inlineStr">
         <is>
-          <t>Timing at 0.50× threshold</t>
+          <t>Timing at 0.5× threshold</t>
         </is>
       </c>
       <c r="H365" s="16" t="n"/>
@@ -36496,7 +36496,7 @@
       </c>
       <c r="G366" s="15" t="inlineStr">
         <is>
-          <t>Timing at 0.50× threshold</t>
+          <t>Timing at 0.5× threshold</t>
         </is>
       </c>
       <c r="H366" s="16" t="n"/>
@@ -37507,7 +37507,7 @@
       </c>
       <c r="G379" s="11" t="inlineStr">
         <is>
-          <t>Timing at 1.30× threshold</t>
+          <t>Timing at 1.3× threshold</t>
         </is>
       </c>
       <c r="H379" s="12" t="n"/>
@@ -37586,7 +37586,7 @@
       </c>
       <c r="G380" s="11" t="inlineStr">
         <is>
-          <t>Timing at 1.30× threshold</t>
+          <t>Timing at 1.3× threshold</t>
         </is>
       </c>
       <c r="H380" s="12" t="n"/>
@@ -37661,7 +37661,7 @@
       </c>
       <c r="G381" s="11" t="inlineStr">
         <is>
-          <t>Timing at 1.30× threshold</t>
+          <t>Timing at 1.3× threshold</t>
         </is>
       </c>
       <c r="H381" s="12" t="n"/>
@@ -37736,7 +37736,7 @@
       </c>
       <c r="G382" s="11" t="inlineStr">
         <is>
-          <t>Timing at 1.30× threshold</t>
+          <t>Timing at 1.3× threshold</t>
         </is>
       </c>
       <c r="H382" s="12" t="n"/>
@@ -37815,7 +37815,7 @@
       </c>
       <c r="G383" s="11" t="inlineStr">
         <is>
-          <t>Timing at 1.30× threshold</t>
+          <t>Timing at 1.3× threshold</t>
         </is>
       </c>
       <c r="H383" s="12" t="n"/>
@@ -37894,7 +37894,7 @@
       </c>
       <c r="G384" s="11" t="inlineStr">
         <is>
-          <t>Timing at 1.30× threshold</t>
+          <t>Timing at 1.3× threshold</t>
         </is>
       </c>
       <c r="H384" s="12" t="n"/>
@@ -40208,7 +40208,7 @@
       </c>
       <c r="F4" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — above</t>
+          <t>Slope at Irest 1 pu — above</t>
         </is>
       </c>
       <c r="G4" s="11" t="inlineStr">
@@ -40317,7 +40317,7 @@
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — below</t>
+          <t>Slope at Irest 1 pu — below</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
@@ -40426,7 +40426,7 @@
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — above</t>
+          <t>Slope at Irest 3 pu — above</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
@@ -40535,7 +40535,7 @@
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — below</t>
+          <t>Slope at Irest 3 pu — below</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
@@ -40644,7 +40644,7 @@
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — above</t>
+          <t>Slope at Irest 8 pu — above</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
@@ -40753,7 +40753,7 @@
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — below</t>
+          <t>Slope at Irest 8 pu — below</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
@@ -40867,7 +40867,7 @@
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
-          <t>Both ends matched and opposed at 8.0 pu — an external fault. This is the polarity and ratio test.</t>
+          <t>Both ends matched and opposed at 8 pu — an external fault. This is the polarity and ratio test.</t>
         </is>
       </c>
       <c r="H10" s="12" t="n"/>
@@ -41295,7 +41295,7 @@
       </c>
       <c r="G14" s="15" t="inlineStr">
         <is>
-          <t>Both ends matched and opposed at 4.0 pu residual</t>
+          <t>Both ends matched and opposed at 4 pu residual</t>
         </is>
       </c>
       <c r="H14" s="16" t="n"/>
@@ -42582,7 +42582,7 @@
       </c>
       <c r="F30" s="15" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="G30" s="15" t="inlineStr">
@@ -42861,7 +42861,7 @@
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr">
@@ -42954,7 +42954,7 @@
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× threshold</t>
+          <t>Timing at 3× threshold</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr">
@@ -43047,7 +43047,7 @@
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× threshold</t>
+          <t>Timing at 5× threshold</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr">
@@ -43326,7 +43326,7 @@
       </c>
       <c r="F38" s="15" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="G38" s="15" t="inlineStr">
@@ -43909,7 +43909,7 @@
       </c>
       <c r="G44" s="15" t="inlineStr">
         <is>
-          <t>Internal fault at end A, 4.0 × In</t>
+          <t>Internal fault at end A, 4 × In</t>
         </is>
       </c>
       <c r="H44" s="16" t="n">
@@ -45631,7 +45631,7 @@
       </c>
       <c r="F63" s="15" t="inlineStr">
         <is>
-          <t>Timing at 0.50× threshold</t>
+          <t>Timing at 0.5× threshold</t>
         </is>
       </c>
       <c r="G63" s="15" t="inlineStr">
@@ -45910,7 +45910,7 @@
       </c>
       <c r="F66" s="11" t="inlineStr">
         <is>
-          <t>Timing at 1.30× threshold</t>
+          <t>Timing at 1.3× threshold</t>
         </is>
       </c>
       <c r="G66" s="11" t="inlineStr">
@@ -47929,7 +47929,7 @@
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — above</t>
+          <t>Slope at Irest 1 pu — above</t>
         </is>
       </c>
       <c r="H20" s="12" t="n"/>
@@ -48008,7 +48008,7 @@
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — above</t>
+          <t>Slope at Irest 1 pu — above</t>
         </is>
       </c>
       <c r="H21" s="12" t="n"/>
@@ -48087,7 +48087,7 @@
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — above</t>
+          <t>Slope at Irest 1 pu — above</t>
         </is>
       </c>
       <c r="H22" s="12" t="n"/>
@@ -48166,7 +48166,7 @@
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — above</t>
+          <t>Slope at Irest 1 pu — above</t>
         </is>
       </c>
       <c r="H23" s="12" t="n"/>
@@ -48249,7 +48249,7 @@
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — above</t>
+          <t>Slope at Irest 1 pu — above</t>
         </is>
       </c>
       <c r="H24" s="12" t="n"/>
@@ -48332,7 +48332,7 @@
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — above</t>
+          <t>Slope at Irest 1 pu — above</t>
         </is>
       </c>
       <c r="H25" s="12" t="n"/>
@@ -48415,7 +48415,7 @@
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — above</t>
+          <t>Slope at Irest 1 pu — above</t>
         </is>
       </c>
       <c r="H26" s="12" t="n"/>
@@ -48498,7 +48498,7 @@
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — above</t>
+          <t>Slope at Irest 1 pu — above</t>
         </is>
       </c>
       <c r="H27" s="12" t="n"/>
@@ -48581,7 +48581,7 @@
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — above</t>
+          <t>Slope at Irest 1 pu — above</t>
         </is>
       </c>
       <c r="H28" s="12" t="n"/>
@@ -48664,7 +48664,7 @@
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — below</t>
+          <t>Slope at Irest 1 pu — below</t>
         </is>
       </c>
       <c r="H29" s="12" t="n"/>
@@ -48743,7 +48743,7 @@
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — below</t>
+          <t>Slope at Irest 1 pu — below</t>
         </is>
       </c>
       <c r="H30" s="12" t="n"/>
@@ -48822,7 +48822,7 @@
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — below</t>
+          <t>Slope at Irest 1 pu — below</t>
         </is>
       </c>
       <c r="H31" s="12" t="n"/>
@@ -48901,7 +48901,7 @@
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — below</t>
+          <t>Slope at Irest 1 pu — below</t>
         </is>
       </c>
       <c r="H32" s="12" t="n"/>
@@ -48984,7 +48984,7 @@
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — below</t>
+          <t>Slope at Irest 1 pu — below</t>
         </is>
       </c>
       <c r="H33" s="12" t="n"/>
@@ -49067,7 +49067,7 @@
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — below</t>
+          <t>Slope at Irest 1 pu — below</t>
         </is>
       </c>
       <c r="H34" s="12" t="n"/>
@@ -49150,7 +49150,7 @@
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — below</t>
+          <t>Slope at Irest 1 pu — below</t>
         </is>
       </c>
       <c r="H35" s="12" t="n"/>
@@ -49233,7 +49233,7 @@
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — below</t>
+          <t>Slope at Irest 1 pu — below</t>
         </is>
       </c>
       <c r="H36" s="12" t="n"/>
@@ -49316,7 +49316,7 @@
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 1.0 pu — below</t>
+          <t>Slope at Irest 1 pu — below</t>
         </is>
       </c>
       <c r="H37" s="12" t="n"/>
@@ -49399,7 +49399,7 @@
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — above</t>
+          <t>Slope at Irest 3 pu — above</t>
         </is>
       </c>
       <c r="H38" s="12" t="n"/>
@@ -49478,7 +49478,7 @@
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — above</t>
+          <t>Slope at Irest 3 pu — above</t>
         </is>
       </c>
       <c r="H39" s="12" t="n"/>
@@ -49557,7 +49557,7 @@
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — above</t>
+          <t>Slope at Irest 3 pu — above</t>
         </is>
       </c>
       <c r="H40" s="12" t="n"/>
@@ -49636,7 +49636,7 @@
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — above</t>
+          <t>Slope at Irest 3 pu — above</t>
         </is>
       </c>
       <c r="H41" s="12" t="n"/>
@@ -49719,7 +49719,7 @@
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — above</t>
+          <t>Slope at Irest 3 pu — above</t>
         </is>
       </c>
       <c r="H42" s="12" t="n"/>
@@ -49802,7 +49802,7 @@
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — above</t>
+          <t>Slope at Irest 3 pu — above</t>
         </is>
       </c>
       <c r="H43" s="12" t="n"/>
@@ -49885,7 +49885,7 @@
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — above</t>
+          <t>Slope at Irest 3 pu — above</t>
         </is>
       </c>
       <c r="H44" s="12" t="n"/>
@@ -49968,7 +49968,7 @@
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — above</t>
+          <t>Slope at Irest 3 pu — above</t>
         </is>
       </c>
       <c r="H45" s="12" t="n"/>
@@ -50051,7 +50051,7 @@
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — above</t>
+          <t>Slope at Irest 3 pu — above</t>
         </is>
       </c>
       <c r="H46" s="12" t="n"/>
@@ -50134,7 +50134,7 @@
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — below</t>
+          <t>Slope at Irest 3 pu — below</t>
         </is>
       </c>
       <c r="H47" s="12" t="n"/>
@@ -50213,7 +50213,7 @@
       </c>
       <c r="G48" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — below</t>
+          <t>Slope at Irest 3 pu — below</t>
         </is>
       </c>
       <c r="H48" s="12" t="n"/>
@@ -50292,7 +50292,7 @@
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — below</t>
+          <t>Slope at Irest 3 pu — below</t>
         </is>
       </c>
       <c r="H49" s="12" t="n"/>
@@ -50371,7 +50371,7 @@
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — below</t>
+          <t>Slope at Irest 3 pu — below</t>
         </is>
       </c>
       <c r="H50" s="12" t="n"/>
@@ -50454,7 +50454,7 @@
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — below</t>
+          <t>Slope at Irest 3 pu — below</t>
         </is>
       </c>
       <c r="H51" s="12" t="n"/>
@@ -50537,7 +50537,7 @@
       </c>
       <c r="G52" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — below</t>
+          <t>Slope at Irest 3 pu — below</t>
         </is>
       </c>
       <c r="H52" s="12" t="n"/>
@@ -50620,7 +50620,7 @@
       </c>
       <c r="G53" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — below</t>
+          <t>Slope at Irest 3 pu — below</t>
         </is>
       </c>
       <c r="H53" s="12" t="n"/>
@@ -50703,7 +50703,7 @@
       </c>
       <c r="G54" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — below</t>
+          <t>Slope at Irest 3 pu — below</t>
         </is>
       </c>
       <c r="H54" s="12" t="n"/>
@@ -50786,7 +50786,7 @@
       </c>
       <c r="G55" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 3.0 pu — below</t>
+          <t>Slope at Irest 3 pu — below</t>
         </is>
       </c>
       <c r="H55" s="12" t="n"/>
@@ -50869,7 +50869,7 @@
       </c>
       <c r="G56" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — above</t>
+          <t>Slope at Irest 8 pu — above</t>
         </is>
       </c>
       <c r="H56" s="12" t="n"/>
@@ -50948,7 +50948,7 @@
       </c>
       <c r="G57" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — above</t>
+          <t>Slope at Irest 8 pu — above</t>
         </is>
       </c>
       <c r="H57" s="12" t="n"/>
@@ -51027,7 +51027,7 @@
       </c>
       <c r="G58" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — above</t>
+          <t>Slope at Irest 8 pu — above</t>
         </is>
       </c>
       <c r="H58" s="12" t="n"/>
@@ -51106,7 +51106,7 @@
       </c>
       <c r="G59" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — above</t>
+          <t>Slope at Irest 8 pu — above</t>
         </is>
       </c>
       <c r="H59" s="12" t="n"/>
@@ -51189,7 +51189,7 @@
       </c>
       <c r="G60" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — above</t>
+          <t>Slope at Irest 8 pu — above</t>
         </is>
       </c>
       <c r="H60" s="12" t="n"/>
@@ -51272,7 +51272,7 @@
       </c>
       <c r="G61" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — above</t>
+          <t>Slope at Irest 8 pu — above</t>
         </is>
       </c>
       <c r="H61" s="12" t="n"/>
@@ -51355,7 +51355,7 @@
       </c>
       <c r="G62" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — above</t>
+          <t>Slope at Irest 8 pu — above</t>
         </is>
       </c>
       <c r="H62" s="12" t="n"/>
@@ -51438,7 +51438,7 @@
       </c>
       <c r="G63" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — above</t>
+          <t>Slope at Irest 8 pu — above</t>
         </is>
       </c>
       <c r="H63" s="12" t="n"/>
@@ -51521,7 +51521,7 @@
       </c>
       <c r="G64" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — above</t>
+          <t>Slope at Irest 8 pu — above</t>
         </is>
       </c>
       <c r="H64" s="12" t="n"/>
@@ -51604,7 +51604,7 @@
       </c>
       <c r="G65" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — below</t>
+          <t>Slope at Irest 8 pu — below</t>
         </is>
       </c>
       <c r="H65" s="12" t="n"/>
@@ -51683,7 +51683,7 @@
       </c>
       <c r="G66" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — below</t>
+          <t>Slope at Irest 8 pu — below</t>
         </is>
       </c>
       <c r="H66" s="12" t="n"/>
@@ -51762,7 +51762,7 @@
       </c>
       <c r="G67" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — below</t>
+          <t>Slope at Irest 8 pu — below</t>
         </is>
       </c>
       <c r="H67" s="12" t="n"/>
@@ -51841,7 +51841,7 @@
       </c>
       <c r="G68" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — below</t>
+          <t>Slope at Irest 8 pu — below</t>
         </is>
       </c>
       <c r="H68" s="12" t="n"/>
@@ -51924,7 +51924,7 @@
       </c>
       <c r="G69" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — below</t>
+          <t>Slope at Irest 8 pu — below</t>
         </is>
       </c>
       <c r="H69" s="12" t="n"/>
@@ -52007,7 +52007,7 @@
       </c>
       <c r="G70" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — below</t>
+          <t>Slope at Irest 8 pu — below</t>
         </is>
       </c>
       <c r="H70" s="12" t="n"/>
@@ -52090,7 +52090,7 @@
       </c>
       <c r="G71" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — below</t>
+          <t>Slope at Irest 8 pu — below</t>
         </is>
       </c>
       <c r="H71" s="12" t="n"/>
@@ -52173,7 +52173,7 @@
       </c>
       <c r="G72" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — below</t>
+          <t>Slope at Irest 8 pu — below</t>
         </is>
       </c>
       <c r="H72" s="12" t="n"/>
@@ -52256,7 +52256,7 @@
       </c>
       <c r="G73" s="11" t="inlineStr">
         <is>
-          <t>Slope at Irest 8.0 pu — below</t>
+          <t>Slope at Irest 8 pu — below</t>
         </is>
       </c>
       <c r="H73" s="12" t="n"/>
@@ -59761,7 +59761,7 @@
       </c>
       <c r="G168" s="15" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H168" s="16" t="n"/>
@@ -59836,7 +59836,7 @@
       </c>
       <c r="G169" s="15" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H169" s="16" t="n"/>
@@ -59911,7 +59911,7 @@
       </c>
       <c r="G170" s="15" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H170" s="16" t="n"/>
@@ -59986,7 +59986,7 @@
       </c>
       <c r="G171" s="15" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H171" s="16" t="n"/>
@@ -60065,7 +60065,7 @@
       </c>
       <c r="G172" s="15" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H172" s="16" t="n"/>
@@ -60144,7 +60144,7 @@
       </c>
       <c r="G173" s="15" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H173" s="16" t="n"/>
@@ -61147,7 +61147,7 @@
       </c>
       <c r="G186" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H186" s="12" t="n"/>
@@ -61222,7 +61222,7 @@
       </c>
       <c r="G187" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H187" s="12" t="n"/>
@@ -61297,7 +61297,7 @@
       </c>
       <c r="G188" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H188" s="12" t="n"/>
@@ -61372,7 +61372,7 @@
       </c>
       <c r="G189" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H189" s="12" t="n"/>
@@ -61451,7 +61451,7 @@
       </c>
       <c r="G190" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H190" s="12" t="n"/>
@@ -61530,7 +61530,7 @@
       </c>
       <c r="G191" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H191" s="12" t="n"/>
@@ -61609,7 +61609,7 @@
       </c>
       <c r="G192" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× threshold</t>
+          <t>Timing at 3× threshold</t>
         </is>
       </c>
       <c r="H192" s="12" t="n"/>
@@ -61684,7 +61684,7 @@
       </c>
       <c r="G193" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× threshold</t>
+          <t>Timing at 3× threshold</t>
         </is>
       </c>
       <c r="H193" s="12" t="n"/>
@@ -61759,7 +61759,7 @@
       </c>
       <c r="G194" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× threshold</t>
+          <t>Timing at 3× threshold</t>
         </is>
       </c>
       <c r="H194" s="12" t="n"/>
@@ -61834,7 +61834,7 @@
       </c>
       <c r="G195" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× threshold</t>
+          <t>Timing at 3× threshold</t>
         </is>
       </c>
       <c r="H195" s="12" t="n"/>
@@ -61913,7 +61913,7 @@
       </c>
       <c r="G196" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× threshold</t>
+          <t>Timing at 3× threshold</t>
         </is>
       </c>
       <c r="H196" s="12" t="n"/>
@@ -61992,7 +61992,7 @@
       </c>
       <c r="G197" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× threshold</t>
+          <t>Timing at 3× threshold</t>
         </is>
       </c>
       <c r="H197" s="12" t="n"/>
@@ -62071,7 +62071,7 @@
       </c>
       <c r="G198" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× threshold</t>
+          <t>Timing at 5× threshold</t>
         </is>
       </c>
       <c r="H198" s="12" t="n"/>
@@ -62146,7 +62146,7 @@
       </c>
       <c r="G199" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× threshold</t>
+          <t>Timing at 5× threshold</t>
         </is>
       </c>
       <c r="H199" s="12" t="n"/>
@@ -62221,7 +62221,7 @@
       </c>
       <c r="G200" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× threshold</t>
+          <t>Timing at 5× threshold</t>
         </is>
       </c>
       <c r="H200" s="12" t="n"/>
@@ -62296,7 +62296,7 @@
       </c>
       <c r="G201" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× threshold</t>
+          <t>Timing at 5× threshold</t>
         </is>
       </c>
       <c r="H201" s="12" t="n"/>
@@ -62375,7 +62375,7 @@
       </c>
       <c r="G202" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× threshold</t>
+          <t>Timing at 5× threshold</t>
         </is>
       </c>
       <c r="H202" s="12" t="n"/>
@@ -62454,7 +62454,7 @@
       </c>
       <c r="G203" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× threshold</t>
+          <t>Timing at 5× threshold</t>
         </is>
       </c>
       <c r="H203" s="12" t="n"/>
@@ -63457,7 +63457,7 @@
       </c>
       <c r="G216" s="15" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H216" s="16" t="n"/>
@@ -63532,7 +63532,7 @@
       </c>
       <c r="G217" s="15" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H217" s="16" t="n"/>
@@ -63607,7 +63607,7 @@
       </c>
       <c r="G218" s="15" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H218" s="16" t="n"/>
@@ -63682,7 +63682,7 @@
       </c>
       <c r="G219" s="15" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H219" s="16" t="n"/>
@@ -63761,7 +63761,7 @@
       </c>
       <c r="G220" s="15" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H220" s="16" t="n"/>
@@ -63840,7 +63840,7 @@
       </c>
       <c r="G221" s="15" t="inlineStr">
         <is>
-          <t>Timing at 2.0× threshold</t>
+          <t>Timing at 2× threshold</t>
         </is>
       </c>
       <c r="H221" s="16" t="n"/>
@@ -74952,7 +74952,7 @@
       </c>
       <c r="G361" s="15" t="inlineStr">
         <is>
-          <t>Timing at 0.50× threshold</t>
+          <t>Timing at 0.5× threshold</t>
         </is>
       </c>
       <c r="H361" s="16" t="n"/>
@@ -75031,7 +75031,7 @@
       </c>
       <c r="G362" s="15" t="inlineStr">
         <is>
-          <t>Timing at 0.50× threshold</t>
+          <t>Timing at 0.5× threshold</t>
         </is>
       </c>
       <c r="H362" s="16" t="n"/>
@@ -75106,7 +75106,7 @@
       </c>
       <c r="G363" s="15" t="inlineStr">
         <is>
-          <t>Timing at 0.50× threshold</t>
+          <t>Timing at 0.5× threshold</t>
         </is>
       </c>
       <c r="H363" s="16" t="n"/>
@@ -75181,7 +75181,7 @@
       </c>
       <c r="G364" s="15" t="inlineStr">
         <is>
-          <t>Timing at 0.50× threshold</t>
+          <t>Timing at 0.5× threshold</t>
         </is>
       </c>
       <c r="H364" s="16" t="n"/>
@@ -75260,7 +75260,7 @@
       </c>
       <c r="G365" s="15" t="inlineStr">
         <is>
-          <t>Timing at 0.50× threshold</t>
+          <t>Timing at 0.5× threshold</t>
         </is>
       </c>
       <c r="H365" s="16" t="n"/>
@@ -75339,7 +75339,7 @@
       </c>
       <c r="G366" s="15" t="inlineStr">
         <is>
-          <t>Timing at 0.50× threshold</t>
+          <t>Timing at 0.5× threshold</t>
         </is>
       </c>
       <c r="H366" s="16" t="n"/>
@@ -76350,7 +76350,7 @@
       </c>
       <c r="G379" s="11" t="inlineStr">
         <is>
-          <t>Timing at 1.30× threshold</t>
+          <t>Timing at 1.3× threshold</t>
         </is>
       </c>
       <c r="H379" s="12" t="n"/>
@@ -76429,7 +76429,7 @@
       </c>
       <c r="G380" s="11" t="inlineStr">
         <is>
-          <t>Timing at 1.30× threshold</t>
+          <t>Timing at 1.3× threshold</t>
         </is>
       </c>
       <c r="H380" s="12" t="n"/>
@@ -76504,7 +76504,7 @@
       </c>
       <c r="G381" s="11" t="inlineStr">
         <is>
-          <t>Timing at 1.30× threshold</t>
+          <t>Timing at 1.3× threshold</t>
         </is>
       </c>
       <c r="H381" s="12" t="n"/>
@@ -76579,7 +76579,7 @@
       </c>
       <c r="G382" s="11" t="inlineStr">
         <is>
-          <t>Timing at 1.30× threshold</t>
+          <t>Timing at 1.3× threshold</t>
         </is>
       </c>
       <c r="H382" s="12" t="n"/>
@@ -76658,7 +76658,7 @@
       </c>
       <c r="G383" s="11" t="inlineStr">
         <is>
-          <t>Timing at 1.30× threshold</t>
+          <t>Timing at 1.3× threshold</t>
         </is>
       </c>
       <c r="H383" s="12" t="n"/>
@@ -76737,7 +76737,7 @@
       </c>
       <c r="G384" s="11" t="inlineStr">
         <is>
-          <t>Timing at 1.30× threshold</t>
+          <t>Timing at 1.3× threshold</t>
         </is>
       </c>
       <c r="H384" s="12" t="n"/>
